--- a/artfynd/A 33229-2025 artfynd.xlsx
+++ b/artfynd/A 33229-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80985636</v>
+        <v>80985100</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>822837.3221486777</v>
+        <v>823039</v>
       </c>
       <c r="R2" t="n">
-        <v>7463921.21599853</v>
+        <v>7464053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80985123</v>
+        <v>80985104</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>823197.1400420277</v>
+        <v>823395</v>
       </c>
       <c r="R3" t="n">
-        <v>7463952.836783233</v>
+        <v>7464265</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80985620</v>
+        <v>80985105</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822810.1373369137</v>
+        <v>823100</v>
       </c>
       <c r="R4" t="n">
-        <v>7463990.196659471</v>
+        <v>7463884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80985623</v>
+        <v>80985106</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>822819.0207996378</v>
+        <v>823079</v>
       </c>
       <c r="R5" t="n">
-        <v>7463984.984348233</v>
+        <v>7464065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80985121</v>
+        <v>80985111</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>823154.2932385076</v>
+        <v>823223</v>
       </c>
       <c r="R6" t="n">
-        <v>7464017.961781099</v>
+        <v>7463906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2019-07-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80985095</v>
+        <v>80985116</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>823320.1851134112</v>
+        <v>823030</v>
       </c>
       <c r="R7" t="n">
-        <v>7464297.950225136</v>
+        <v>7464051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2019-07-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,1170 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80985119</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>823076</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7463861</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>80985121</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>823154</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7464018</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>80985123</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>823197</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7463953</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>80985636</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>822837</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7463921</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>80985620</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>822810</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7463990</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>80985621</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>822696</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7463802</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>80985622</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>822702</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7464122</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>80985623</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>822819</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7463985</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>80985136</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>823045</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7464066</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80985138</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>823084</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7464086</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>80985140</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>823079</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7464065</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>80985078</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Selkävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>823045</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7464066</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
